--- a/public/documents/pieces-reponse-2/R2-ventes-sans-achat.xlsx
+++ b/public/documents/pieces-reponse-2/R2-ventes-sans-achat.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calcul" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Méthode" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code 2091" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="p75 vs annexes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0&quot;×&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00 %"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +50,15 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7EFD9"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,6 +151,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -527,7 +550,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Achats : 199 factures du fournisseur Franche-Comté Boissons Services, rattachées par CODE ARTICLE et par date de facture. Ventes : annexes de caisse C/D (format de service × contenance). Stocks : inventaires physiques de clôture (31/03). Prix de vente : ANNEXE-B1 (prix-vente 2022-2023). ⚠ Annexes primaires de caisse disponibles pour 2022-2023 uniquement ; 2023-2024 et 2024-2025 reposent sur l'extraction de la réponse n°1 et appellent la production des annexes C-2/D-2 et C-3/D-3.</t>
+          <t>Achats : 199 factures du fournisseur Franche-Comté Boissons Services, rattachées par CODE ARTICLE et par date de facture. Ventes : annexes de caisse B/D des trois exercices (ANNEXE-B1/C1 2022-2023 ; ANNEXE-B2/D2 2023-2024 ; ANNEXE-B3/D3 2024-2025), format de service × contenance. Stocks : inventaires physiques de clôture (31/03). Prix de vente : ANNEXE-B1. Les volumes 2023-2024 et 2024-2025 ont été revérifiés sur les annexes D2/D3 (synthèse produit) : 5 310 cl et 4 683 cl, identiques aux totaux des annexes du service du 18/05/2026 (p. 63 et p. 77).</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2669,7 @@
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Rappel — HC de Beaune rouge réellement en caisse (annexes/extraction) : 2022-2023 = 7 218 cl ; 2023-2024 = 5 310 cl ; 2024-2025 = 4 683 cl. La ligne blanc 12 950 cl n'est pas reproductible (caisse : 150 cl en 2023-2024, 0 en 2024-2025) et le service la limite lui-même au seul exercice 2023-2024 (Proposition p.32).</t>
+          <t>Rappel : HC de Beaune rouge en caisse : 2022-2023 = 7 218 cl (notre extraction ; l'annexe du service du 18/05/2026 p. 48 totalise 7 255 cl, écart 37 cl = une demi-bouteille comptée 1) ; 2023-2024 = 5 310 cl ; 2024-2025 = 4 683 cl. La ligne « Beaune BLANC 12 950 cl » se décompose en 150 cl de pichets « C.DE BEAUNE B » et 12 800 cl de « PICHET ROSE » portés par le même code 2091 (voir onglet « Code 2091 »).</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2798,6 +2821,1539 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Code 2091</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Les 12 950 cl de « Beaune BLANC » sont la somme des lignes du code de caisse 2091 dans l'annexe D-2 du service : 3 pichets « C.DE BEAUNE B » à 30 € (150 cl) et 256 pichets « PICHET ROSE » à 10,49 € de moyenne (12 800 cl). Le code 2091 a été réaffecté au rosé maison le 05/05/2023 (dernière vente Beaune B le 30/04/2023). Le service a imprimé cette ligne de 256 pichets, avec son prix de 10,49 €, sous le libellé « PICHET C.DE BEAUNE B » (annexe 18/05 p. 64) et l'a rangée dans un bloc à disponible nul. Le rosé maison est acheté en BIB (23 BIB de 10 L en 2023-2024).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>p. 75</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Les volumes imprimés p. 75 sont ceux des annexes du 18/05 : « exercice 1 » = 5 400 / 4 683 = 2024-2025 (p. 77) ; « exercice 2 » = 6 300 / 5 310 = 2023-2024 (p. 63) ; « exercice 3 » = copie de l'exercice 2. Le vrai 2022-2023 (8 475 / 7 255, p. 48) n'y figure pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Annexes caisse</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Les annexes B/D des trois exercices sont disponibles ; les volumes 2023-2024 (5 310 cl) et 2024-2025 (4 683 cl) sont vérifiés sur D2/D3 et coïncident avec les annexes du service.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>D'OÙ VIENNENT LES 12 950 cl : le code de caisse 2091 porte deux libellés successifs</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source : ANNEXE-D2_synthese-produit_2023-2024.xls (fichier du service, colonnes Ref_prd / Lib_ticket / Uprice_wt / Prix moyen / Qte / Tot_rem Ttc), lignes du code 2091 ; ANNEXE-B2 (lignes de tickets) pour les dates ; annexe du 18/05/2026 p. 64 pour la lecture faite par le service.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>A. Lignes du code 2091 dans l'annexe D-2 (2023-2024)</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Prix unitaire TTC (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Total TTC (€) = prix × qté</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Contenance retenue par le service (cl)</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Volume (cl) = qté × contenance</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>PICHET C.DE BEAUNE B (ligne 145 de D-2)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <f>B5*C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="2">
+        <f>C5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>pichet de Hautes Côtes de Beaune blanc, 30 € : réel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PICHET ROSE (ligne 146 de D-2)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <f>B6*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2">
+        <f>C6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>pichet de rosé maison (BIB), même code 2091</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PICHET ROSE (ligne 147 de D-2)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="D7" s="2">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2">
+        <f>C7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>pichet de rosé maison (BIB), même code 2091</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL code 2091 (ce que le service a lu comme « Haute côte de Beaune BLANC »)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="2">
+        <f>SUM(D5:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>dont PICHET ROSE : quantité, total TTC, volume</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2">
+        <f>C6+C7</f>
+        <v/>
+      </c>
+      <c r="D9" s="2">
+        <f>D6+D7</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2">
+        <f>F6+F7</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Prix moyen du PICHET ROSE (€) = total ÷ quantité (le service imprime « 10,49 € », annexe 18/05 p. 64)</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <f>D9/C9</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Part du rosé dans les 12 950 cl (le service imprime « 98,84 % »)</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <f>F9/F8</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Part du vrai Beaune blanc dans les 12 950 cl (le service imprime « 1,16 % »)</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <f>F5/F8</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Contrôle : total = 12 950 cl imprimé p. 75 et p. 64 ?</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <f>IF(F8=12950,"OUI","NON")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>B. Chronologie du code 2091 (ANNEXE-B2, lignes de tickets 2023-2024)</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Lignes</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Unités</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>Montant TTC (€)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Dernière vente sous le libellé « PICHET C.DE BEAUNE B »</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>30/04/2023</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>PICHET C.DE BEAUNE B</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Première vente sous le libellé « PICHET ROSE » (même code 2091)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>05/05/2023</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>PICHET ROSE</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Dernière vente « PICHET ROSE » de l'exercice</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2024</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>PICHET ROSE</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2665</v>
+      </c>
+      <c r="G18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Note : l'annexe D-2 (synthèse) retient 256 unités / 2 686,00 € pour le rosé (nettes de remises et demi-pichets) ; l'annexe B-2 (lignes) en compte 257 lignes / 262 unités / 2 665,00 €. C'est la lecture D-2 (256 ; 10,49 €) que le service a imprimée.</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025 (ANNEXE-D3, lignes 149-150) : le code 2091 ne porte plus que « PICHET ROSE »</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="D21" s="2">
+        <f>B21*C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Total pichets rosé 2024-2025 (unités ; volume à 50 cl)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2">
+        <f>C20+C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2">
+        <f>C22*50</f>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Pichets « C.DE BEAUNE B » vendus en 2024-2025</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2">
+        <f>C23*50</f>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>C. Le rosé maison est acheté (BIB), factures FCBS par exercice</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>BIB 10 L (unités)</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>BIB 5 L / 3 L (unités)</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Volume acheté (cl)</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Pichets rosé vendus (unités)</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>Volume vendu (cl) = unités × 50</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Couverture achats ÷ ventes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024 : BIB COTES DE PROV ROSE 10 L (code 603042) = 23 ; le service lit lui-même « BIB 10 L Provence Rosé 23 » + « BIB 5 L 8 » (annexe 18/05, tableau des achats 2023-2024)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <f>B26*1000+C26*500</f>
+        <v/>
+      </c>
+      <c r="E26" s="2">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="F26" s="2">
+        <f>E26*50</f>
+        <v/>
+      </c>
+      <c r="G26" s="2">
+        <f>D26/F26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025 : BIB COTES DE PROVENCE 10 L ROSE (601956) = 16 ; BIB GARDILLES ROSE 10 L (605168) = 1 ; BIB 3 L ROSE (665048) = 4</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27*1000+C27*300</f>
+        <v/>
+      </c>
+      <c r="E27" s="2">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="F27" s="2">
+        <f>E27*50</f>
+        <v/>
+      </c>
+      <c r="G27" s="2">
+        <f>D27/F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Lecture : les 256 pichets de 2023-2024 sont du rosé maison tiré de BIB achetés et facturés ; ils n'ont rien à voir avec le Hautes Côtes de Beaune blanc. Le service les a comptés dans le bloc « Beaune blanc » (disponible 0) et non dans le bloc « pichets de vin maison » où figure le disponible des BIB rosé : d'où 12 800 cl « vendus sans achat ».</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>D. Test de prix</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Prix (€ TTC)</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Rapport</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl de Hautes Côtes de Beaune blanc (ANNEXE-B1/B2, code 2091 jusqu'au 30/04/2023)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Prix moyen imprimé par le service pour la ligne de 256 pichets (annexe 18/05 p. 64)</t>
+        </is>
+      </c>
+      <c r="B32" s="2">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Rapport prix Beaune blanc ÷ prix de la ligne de 256 : un pichet de Beaune à 30 € ne se vend pas 10,49 €</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2">
+        <f>B31/B32</f>
+        <v/>
+      </c>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>LES VOLUMES DE LA PAGE 75 (04/09/2026) RAPPROCHÉS DES ANNEXES « PAR PRODUIT » DU 18/05/2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sources : réponse du service du 04/09/2026 p. 75 (trois tableaux) ; proposition du 18/05/2026, annexes boissons : tableau des achats/stocks/disponibles (p. 29 pour 2022-2023, puis 2023-2024 et 2024-2025) et blocs Haute côte Beaune rouge (p. 48, p. 63, p. 77), Bordeaux (p. 49, p. 63, p. 77), Haute côte Nuit blanc (p. 49, p. 64, p. 78). Valeurs saisies = lecture des annexes ; résultats = formules.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>A. Haute côte de Beaune ROUGE, exercice réel (annexes 18/05)</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Achats FCBS (bt)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Stock 31/03 N-1 (bt)</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Stock 31/03 N (bt)</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Disponible (bt) = achats + SI − SF</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Disponible (cl) = bt × 75</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Caisse (cl) selon l'annexe</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>Disponible − caisse (cl)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2022-2023 (p. 29 et p. 48)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2">
+        <f>B5+C5-D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>E5*75</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>7255</v>
+      </c>
+      <c r="H5" s="2">
+        <f>F5-G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024 (p. 63)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2">
+        <f>B6+C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>E6*75</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>5310</v>
+      </c>
+      <c r="H6" s="2">
+        <f>F6-G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025 (p. 77)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2">
+        <f>B7+C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>E7*75</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>4683</v>
+      </c>
+      <c r="H7" s="2">
+        <f>F7-G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Caisse 2022-2023 = somme des cinq lignes de l'annexe p. 48 : 495 + 2 235 + 1 300 + 2 625 + 600 (les pourcentages imprimés 6,82 / 30,81 / 17,92 / 36,18 / 8,27 % se recalculent sur ce total)</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <f>495+2235+1300+2625+600</f>
+        <v/>
+      </c>
+      <c r="C8" s="2">
+        <f>ROUND(495/B8*100,2)</f>
+        <v/>
+      </c>
+      <c r="D8" s="2">
+        <f>ROUND(2235/B8*100,2)</f>
+        <v/>
+      </c>
+      <c r="E8" s="2">
+        <f>ROUND(1300/B8*100,2)</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>ROUND(2625/B8*100,2)</f>
+        <v/>
+      </c>
+      <c r="G8" s="2">
+        <f>ROUND(600/B8*100,2)</f>
+        <v/>
+      </c>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Part « disparue » 2022-2023 selon le service (14,4 % dans son tableau des disparus) = (disponible − caisse) ÷ disponible</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <f>H5/F5</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>B. Ce que la page 75 imprime, et à quel exercice réel cela correspond</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Disponible imprimé (cl)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Caisse imprimée (cl)</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Exercice réel ayant ces valeurs</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Disponible réel de l'exercice annoncé (cl)</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Caisse réelle de l'exercice annoncé (cl)</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Même disponible ?</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>Même caisse ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>« Exercice 1 » (annoncé 2022-2023)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4683</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025 (p. 77)</t>
+        </is>
+      </c>
+      <c r="E12" s="2">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="F12" s="2">
+        <f>G5</f>
+        <v/>
+      </c>
+      <c r="G12" s="2">
+        <f>IF(B12=E12,"oui","NON")</f>
+        <v/>
+      </c>
+      <c r="H12" s="2">
+        <f>IF(C12=F12,"oui","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>« Exercice 2 » (annoncé 2023-2024)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>6300</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024 (p. 63)</t>
+        </is>
+      </c>
+      <c r="E13" s="2">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="F13" s="2">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="G13" s="2">
+        <f>IF(B13=E13,"oui","NON")</f>
+        <v/>
+      </c>
+      <c r="H13" s="2">
+        <f>IF(C13=F13,"oui","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>« Exercice 3 » (annoncé 2024-2025)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>6300</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>5310</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024 (p. 63), repris une seconde fois</t>
+        </is>
+      </c>
+      <c r="E14" s="2">
+        <f>F7</f>
+        <v/>
+      </c>
+      <c r="F14" s="2">
+        <f>G7</f>
+        <v/>
+      </c>
+      <c r="G14" s="2">
+        <f>IF(B14=E14,"oui","NON")</f>
+        <v/>
+      </c>
+      <c r="H14" s="2">
+        <f>IF(C14=F14,"oui","NON")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Contrôle : « Exercice 1 » = valeurs de 2024-2025 ?</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <f>IF(AND(B12=F7,C12=G7),"OUI","non")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Contrôle : « Exercice 3 » = « Exercice 2 » (copie) ?</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <f>IF(AND(B14=B13,C14=C13),"OUI","non")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>C. Les trois blocs globalisés, exercice par exercice, avec les disponibles du service et la caisse corrigée du rosé</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Disponible rouge (cl)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Disponible Bordeaux (cl)</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Disponible blanc (cl)</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Caisse rouge (cl)</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Caisse Bordeaux (cl)</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>Caisse blanc corrigée (cl)</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>Disponible total − caisse totale (cl)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2022-2023 (annexes p. 29, 48, 49)</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="C19" s="2">
+        <f>10*75</f>
+        <v/>
+      </c>
+      <c r="D19" s="2">
+        <f>42*75</f>
+        <v/>
+      </c>
+      <c r="E19" s="2">
+        <f>G5</f>
+        <v/>
+      </c>
+      <c r="F19" s="2">
+        <f>9*75</f>
+        <v/>
+      </c>
+      <c r="G19" s="2">
+        <f>6*50+3*75</f>
+        <v/>
+      </c>
+      <c r="H19" s="2">
+        <f>B19+C19+D19-E19-F19-G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2023-2024 (annexes p. 63, 64) : blanc = 3 pichets réels (150 cl), le rosé (12 800 cl) remis dans son bloc</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <f>'Code 2091'!F5</f>
+        <v/>
+      </c>
+      <c r="H20" s="2">
+        <f>B20+C20+D20-E20-F20-G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025 (annexes p. 77, 78)</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <f>F7</f>
+        <v/>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <f>G7</f>
+        <v/>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <f>B21+C21+D21-E21-F21-G21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Lecture : une fois le rosé remis dans son bloc, le disponible des trois vins dépasse la caisse sur chacun des trois exercices : il n'existe aucun exercice où « les ventes dépassent le disponible ».</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Tableau du service, exercices 2 et 3 : écart imprimé 11 960 cl ; recalcul avec la caisse blanc corrigée (5 310 + 0 + 150 = 5 460 cl)</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <f>E20+F20+G20</f>
+        <v/>
+      </c>
+      <c r="C23" s="2">
+        <f>B20-B23</f>
+        <v/>
+      </c>
+      <c r="D23" s="2">
+        <f>C23/B20</f>
+        <v/>
+      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Taux imprimé 65,49 % : recalcul 11 960 ÷ 18 260</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <f>11960/18260</f>
+        <v/>
+      </c>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>D. Les deux vins nommés dans le grief, dans les propres annexes du service (18/05, p. 29 et p. 49)</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Achats FCBS (bt)</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Stock 31/03/22 (bt)</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Stock 31/03/23 (bt)</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Disponible (bt)</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Caisse 2022-2023 (cl)</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Disponible (cl)</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>Disponible − caisse (cl)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>« Bordeaux 75 cl » (= Bordeaux Supérieur Château Grand Renom, bouton MOUTON CADET)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <f>B27+C27-D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="2">
+        <f>9*75</f>
+        <v/>
+      </c>
+      <c r="G27" s="2">
+        <f>E27*75</f>
+        <v/>
+      </c>
+      <c r="H27" s="2">
+        <f>G27-F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>« Haute côte Nuit blanc 75 cl » (= HC de Nuits blanc Lupé Cholet ; le service compte 25 achetées, nos factures 24)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <f>B28+C28-D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="2">
+        <f>6*50+3*75</f>
+        <v/>
+      </c>
+      <c r="G28" s="2">
+        <f>E28*75</f>
+        <v/>
+      </c>
+      <c r="H28" s="2">
+        <f>G28-F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Lecture : pour les deux vins cités comme « vendus sans aucun achat », le service avait lui-même identifié les achats (11 et 25 bouteilles) et un disponible supérieur aux ventes. La bouteille de Bordeaux non retrouvée (H27 = 75 cl) est la seule sortie non expliquée.</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>C-A « reconstitué » de ces blocs dans la méthode par produit du 18/05 : Bordeaux 2022-2023 = 10 bt × 33,82 € TTC ; Nuits blanc 2022-2023 = 36 pichets × 30 € + 18 bt × 39,50 € ; blanc 2023-2024 (disponible 0) = 0 €</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <f>10*33.82</f>
+        <v/>
+      </c>
+      <c r="C30" s="2">
+        <f>B30/1.2</f>
+        <v/>
+      </c>
+      <c r="D30" s="2">
+        <f>36*30+18*39.5</f>
+        <v/>
+      </c>
+      <c r="E30" s="2">
+        <f>D30/1.2</f>
+        <v/>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Lecture : dans cette méthode, un bloc où les ventes dépassent le disponible produit 0 € (disponible nul) ; seuls les blocs à disponible supérieur aux ventes produisent un montant. C'est ce que le service confirme p. 74 : les « ventes sans achat » n'ont entraîné aucun chiffre d'affaires reconstitué.</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
